--- a/data/clean/rechazos_db_OK.xlsx
+++ b/data/clean/rechazos_db_OK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\off_line_files\licencias_dsp\data\clean\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB83D3C5-D24E-49C5-B10E-3EFA7301B1A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5D8476-78B8-49B0-B85E-1516D82094DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16485" windowWidth="29040" windowHeight="15720" xr2:uid="{17F22AF8-9D9B-421E-98C4-6BE7B47CA718}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>anho</t>
   </si>
@@ -97,6 +97,45 @@
   </si>
   <si>
     <t>edad_25-34_fonasa</t>
+  </si>
+  <si>
+    <t>edad_35-44_fonasa</t>
+  </si>
+  <si>
+    <t>edad_45-54_fonasa</t>
+  </si>
+  <si>
+    <t>edad_55-64_fonasa</t>
+  </si>
+  <si>
+    <t>edad_65more_fonasa</t>
+  </si>
+  <si>
+    <t>edad_sin_info_fonasa</t>
+  </si>
+  <si>
+    <t>edad_19less_isapre</t>
+  </si>
+  <si>
+    <t>edad_20-24_isapre</t>
+  </si>
+  <si>
+    <t>edad_25-34_isapre</t>
+  </si>
+  <si>
+    <t>edad_35-44_isapre</t>
+  </si>
+  <si>
+    <t>edad_45-54_isapre</t>
+  </si>
+  <si>
+    <t>edad_55-64_isapre</t>
+  </si>
+  <si>
+    <t>edad_65more_isapre</t>
+  </si>
+  <si>
+    <t>edad_sin_info_isapre</t>
   </si>
 </sst>
 </file>
@@ -132,8 +171,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment textRotation="45" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -468,51 +513,109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{159F80FA-30FB-423D-A8AB-2F0F7D921B06}">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:AA1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="15" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:27" s="2" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>19</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
